--- a/data/dividends_info_20260628.xlsx
+++ b/data/dividends_info_20260628.xlsx
@@ -3178,7 +3178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3660,7 +3660,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3721,14 +3721,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3813,7 +3813,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3925,14 +3925,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3976,14 +3976,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4017,7 +4017,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4085,7 +4085,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4095,14 +4095,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4265,14 +4265,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4350,14 +4350,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4384,19 +4384,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4408,46 +4408,46 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4476,97 +4476,97 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4578,24 +4578,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4629,7 +4629,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4656,22 +4656,192 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nexi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Fiera Milano S.p.A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Eni S.p.A.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cyberoo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>INWIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Analyst Presentation</t>
         </is>
@@ -4701,282 +4871,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cyberoo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>